--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,12 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1937,12 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102971</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102954</v>
+        <v>102960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102960</v>
+        <v>102963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102963</v>
+        <v>102971</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102971</v>
+        <v>102972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102972</v>
+        <v>102973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102973</v>
+        <v>102974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102974</v>
+        <v>102982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 4930-2025 artfynd.xlsx
+++ b/artfynd/A 4930-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>120504264</v>
       </c>
       <c r="B8" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>120504246</v>
       </c>
       <c r="B14" t="n">
-        <v>102982</v>
+        <v>103075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
